--- a/artfynd/A 32157-2025 artfynd.xlsx
+++ b/artfynd/A 32157-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419304</v>
+        <v>123419307</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598524</v>
+        <v>598465</v>
       </c>
       <c r="R2" t="n">
-        <v>6825828</v>
+        <v>6825794</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2345</t>
+          <t>2024_2342</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,15 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419314</v>
+        <v>123419315</v>
       </c>
       <c r="B3" t="n">
-        <v>98019</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,26 +811,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223591</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -854,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598538</v>
+        <v>598455</v>
       </c>
       <c r="R3" t="n">
-        <v>6825737</v>
+        <v>6825632</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +874,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2335</t>
+          <t>2024_2334</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,42 +925,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419311</v>
+        <v>123419309</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -984,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598480</v>
+        <v>598465</v>
       </c>
       <c r="R4" t="n">
-        <v>6825786</v>
+        <v>6825788</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +999,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2338</t>
+          <t>2024_2340</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,12 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:36</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>rikligt i området</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,42 +1050,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419309</v>
+        <v>123419304</v>
       </c>
       <c r="B5" t="n">
-        <v>98135</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1119,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598465</v>
+        <v>598524</v>
       </c>
       <c r="R5" t="n">
-        <v>6825788</v>
+        <v>6825828</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1124,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2340</t>
+          <t>2024_2345</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1159,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1169,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,47 +1175,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419307</v>
+        <v>123419311</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1249,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598465</v>
+        <v>598480</v>
       </c>
       <c r="R6" t="n">
-        <v>6825794</v>
+        <v>6825786</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2342</t>
+          <t>2024_2338</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1289,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1299,7 +1269,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>rikligt i området</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1333,12 +1308,7 @@
         <v>123419312</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1453,6 +1423,131 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123419314</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Öster-Åcka, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>598538</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6825737</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2024_2335</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>
